--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/COLORADO_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/COLORADO_2015.xlsx
@@ -1813,7 +1813,7 @@
         <v>19</v>
       </c>
       <c r="D81">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="82">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C198">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C322">
@@ -6493,7 +6493,7 @@
         <v>19</v>
       </c>
       <c r="D341">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="342">
@@ -6691,7 +6691,7 @@
         <v>19</v>
       </c>
       <c r="D352">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="353">
@@ -6871,7 +6871,7 @@
         <v>19</v>
       </c>
       <c r="D362">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="363">
@@ -7645,7 +7645,7 @@
         <v>19</v>
       </c>
       <c r="D405">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="406">
@@ -11785,7 +11785,7 @@
         <v>19</v>
       </c>
       <c r="D635">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="636">
@@ -12163,7 +12163,7 @@
         <v>19</v>
       </c>
       <c r="D656">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="657">
@@ -13207,7 +13207,7 @@
         <v>19</v>
       </c>
       <c r="D714">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="715">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C795">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C796">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C818">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C819">
@@ -20551,7 +20551,7 @@
         <v>19</v>
       </c>
       <c r="D1122">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="1123">
@@ -23827,7 +23827,7 @@
         <v>19</v>
       </c>
       <c r="D1304">
-        <v>0.0009388279474256349</v>
+        <v>0.0009388279474256348</v>
       </c>
     </row>
     <row r="1305">
